--- a/Result/profitability/2108.xlsx
+++ b/Result/profitability/2108.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.75</v>
       </c>
       <c r="M2" t="n">
-        <v>0.31625</v>
+        <v>0.4025</v>
       </c>
       <c r="N2" t="n">
-        <v>22.7525</v>
+        <v>24.44125</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -681,7 +681,7 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.72</v>
       </c>
       <c r="M3" t="n">
-        <v>0.375</v>
+        <v>0.44875</v>
       </c>
       <c r="N3" t="n">
-        <v>23.32</v>
+        <v>24.93625</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.68</v>
       </c>
       <c r="M4" t="n">
-        <v>0.41625</v>
+        <v>0.495</v>
       </c>
       <c r="N4" t="n">
-        <v>23.4225</v>
+        <v>24.53375</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.05</v>
       </c>
       <c r="M5" t="n">
-        <v>0.37125</v>
+        <v>0.485</v>
       </c>
       <c r="N5" t="n">
-        <v>21.08375</v>
+        <v>22.9325</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.47</v>
       </c>
       <c r="M6" t="n">
-        <v>0.42625</v>
+        <v>0.5137499999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>22.1025</v>
+        <v>23.34875</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.62</v>
       </c>
       <c r="M7" t="n">
-        <v>0.47375</v>
+        <v>0.55875</v>
       </c>
       <c r="N7" t="n">
-        <v>23.1425</v>
+        <v>24.07875</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1279,7 +1279,7 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.36</v>
       </c>
       <c r="M8" t="n">
-        <v>0.48625</v>
+        <v>0.56125</v>
       </c>
       <c r="N8" t="n">
-        <v>22.86</v>
+        <v>23.5525</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1518,7 +1518,7 @@
         <v>0.39</v>
       </c>
       <c r="M9" t="n">
-        <v>0.4925</v>
+        <v>0.4924999999999999</v>
       </c>
       <c r="N9" t="n">
         <v>21.6225</v>
@@ -1645,7 +1645,7 @@
         <v>0.33</v>
       </c>
       <c r="M10" t="n">
-        <v>0.44</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="N10" t="n">
         <v>20.42125</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2108</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>3451</v>
+      </c>
+      <c r="D75" t="n">
+        <v>2320</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1131</v>
+      </c>
+      <c r="F75" t="n">
+        <v>32.78</v>
+      </c>
+      <c r="G75" t="n">
+        <v>682</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>19.75%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>87</v>
+      </c>
+      <c r="J75" t="n">
+        <v>769</v>
+      </c>
+      <c r="K75" t="n">
+        <v>463</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="N75" t="n">
+        <v>23.64</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.5999999999999999</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1.764705882352941</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>5.540000000000003</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.2033773861967696</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.9099999999999999</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>14.79</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.822123401889939</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
